--- a/stories/arbres/ATOM-VIV.PLA.001-07.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gaston est à la fenêtre. Le basilic est dans un pot. Les feuilles sentent fort. Maman, l'adulte, prend l'arrosoir. Maman dit : la plante a besoin d'eau. Elle a besoin de lumière. Gaston tient l'arrosoir avec maman. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Papa ouvre le store. La lumière arrive. Gaston pose l'arrosoir. L'adulte est là.</t>
+          <t>Gaston est à la fenêtre. Le basilic est dans un pot. Les feuilles sentent fort. Maman, l'adulte, prend l'arrosoir. La plante a besoin d'eau. Elle a besoin de lumière. Gaston tient l'arrosoir avec maman. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Papa ouvre le store. La lumière arrive. Gaston pose l'arrosoir. L'adulte est là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gaston est à la fenêtre. Le basilic est dans un pot. Les feuilles sentent fort. Maman, l'adulte, prend l'arrosoir.
+maman|La plante a besoin d'eau. Elle a besoin de lumière.
+narrateur|Gaston tient l'arrosoir avec maman. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Papa ouvre le store. La lumière arrive. Gaston pose l'arrosoir. L'adulte est là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Gaston s'occupe du basilic. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gaston a arrosé. Il y a de l'eau et de la lumière. Maman, l'adulte, était là. Papa a ouvert le store.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Gaston essuie ses mains. Le basilic brille.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-07.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Gaston tient l'arrosoir avec maman. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Papa ouvre le store. La lumière arrive. Gaston pose l'arrosoir. L'adulte est là.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,7 @@
           <t>narrateur|Gaston s'occupe du basilic. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1677,7 @@
           <t>narrateur|Gaston a arrosé. Il y a de l'eau et de la lumière. Maman, l'adulte, était là. Papa a ouvert le store.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Gaston essuie ses mains. Le basilic brille.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.PLA.001-07.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gaston arrose le basilic</t>
+          <t>Le basilic du matin et du soir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss veut du basilic sur les tomates du soir. Le matin, la terre est sèche. Ils arrosent un peu. Le soir, le dessus est encore sec. Un peu d'eau, le store s'ouvre.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gaston est à la fenêtre. Le basilic est dans un pot. Les feuilles sentent fort. Maman, l'adulte, prend l'arrosoir. La plante a besoin d'eau. Elle a besoin de lumière. Gaston tient l'arrosoir avec maman. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Papa ouvre le store. La lumière arrive. Gaston pose l'arrosoir. L'adulte est là.</t>
+          <t>Le store de la cuisine claque un peu. Un filet de jour passe dessous. Ça sent le pain grillé. Le basilic est dans son pot, près du store. Aniss vit ici, avec maman et papa. Tu as vu la terre ? Elle est claire. Le matin, il a souvent soif. Ce soir, les tomates. Je veux l'odeur dessus. Alors on l'aide, ce matin. Tu prends l'arrosoir ? En ce moment, Aniss glisse l'arrosoir. Le plastique est froid, encore. Maman pose la main sur l'anse. L'eau tombe, un filet mince. Un rond sombre s'ouvre au milieu. Il boit. Un peu, pas tout le seau. Le soir, on regardera encore. Encore ? Parfois le dessus sèche deux fois. Aniss pose l'arrosoir. Une feuille se redresse, à peine. C'est le matin. Il a le temps. Le store claque encore, plus loin. Le pain grillé refroidit dans l'assiette. Tu as fini ton pain ? Oui. Aniss essuie une miette. La miette tombe près du pot.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gaston est à la fenêtre. Le basilic est dans un pot. Les feuilles sentent fort. Maman, l'adulte, prend l'arrosoir. Maman dit : la plante a besoin d'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Elle a besoin de lumière. Gaston tient l'arrosoir avec maman. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Papa ouvre le store. La lumière arrive. Gaston pose l'arrosoir. L'adulte est là.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le store de la cuisine claque un peu. Un filet de jour passe dessous. Ça sent le pain grillé. Le basilic est dans son pot, près du store. Aniss vit ici, avec maman et papa. Tu as vu la terre ? Elle est claire. Le matin, il a souvent soif. Ce soir, les tomates. Je veux l'odeur dessus. Alors on l'aide, ce matin. Tu prends l'arrosoir ? En ce moment, Aniss glisse l'arrosoir. Le plastique est froid, encore. Maman pose la main sur l'anse. L'eau tombe, un filet mince. Un rond sombre s'ouvre au milieu. Il boit. Un peu, pas tout le seau. Le soir, on regardera encore. Encore ? Parfois le dessus sèche deux fois. Aniss pose l'arrosoir. Une feuille se redresse, à peine. C'est le matin. Il a le temps. Le store claque encore, plus loin. Le pain grillé refroidit dans l'assiette. Tu as fini ton pain ? Oui. Aniss essuie une miette. La miette tombe près du pot.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,9 +1324,38 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gaston est à la fenêtre. Le basilic est dans un pot. Les feuilles sentent fort. Maman, l'adulte, prend l'arrosoir.
-maman|La plante a besoin d'eau. Elle a besoin de lumière.
-narrateur|Gaston tient l'arrosoir avec maman. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Papa ouvre le store. La lumière arrive. Gaston pose l'arrosoir. L'adulte est là.</t>
+          <t>narrateur|Le store de la cuisine claque un peu.
+narrateur|Un filet de jour passe dessous.
+narrateur|Ça sent le pain grillé.
+narrateur|Le basilic est dans son pot, près du store.
+narrateur|Aniss vit ici, avec maman et papa.
+maman|Tu as vu la terre ?
+enfant-m|Elle est claire.
+papa|Le matin, il a souvent soif.
+enfant-m|Ce soir, les tomates.
+enfant-m|Je veux l'odeur dessus.
+maman|Alors on l'aide, ce matin.
+maman|Tu prends l'arrosoir ?
+narrateur|En ce moment, Aniss glisse l'arrosoir.
+narrateur|Le plastique est froid, encore.
+narrateur|Maman pose la main sur l'anse.
+narrateur|L'eau tombe, un filet mince.
+narrateur|Un rond sombre s'ouvre au milieu.
+enfant-m|Il boit.
+papa|Un peu, pas tout le seau.
+maman|Le soir, on regardera encore.
+enfant-m|Encore ?
+papa|Parfois le dessus sèche deux fois.
+narrateur|Aniss pose l'arrosoir.
+narrateur|Une feuille se redresse, à peine.
+maman|C'est le matin.
+maman|Il a le temps.
+narrateur|Le store claque encore, plus loin.
+narrateur|Le pain grillé refroidit dans l'assiette.
+papa|Tu as fini ton pain ?
+enfant-m|Oui.
+narrateur|Aniss essuie une miette.
+narrateur|La miette tombe près du pot.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,12 +1387,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Gaston s'occupe du basilic. Que fait-il ?</t>
+          <t>Aniss s'occupe du basilic. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Gaston s'occupe du basilic. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss s'occupe du basilic. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1381,7 +1422,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il arrose avec l'adulte. Que fait Gaston ?</t>
+          <t>Il arrose avec l'adulte. Que fait Aniss ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1430,7 +1471,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,10 +1543,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Gaston s'occupe du basilic. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss s'occupe du basilic.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,12 +1571,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gaston a arrosé. Il y a de l'eau et de la lumière. Maman, l'adulte, était là. Papa a ouvert le store.</t>
+          <t>Le soir, la cuisine est orange. Les tomates attendent dans le plat. Le basilic. Aniss touche la terre. Le dessus est encore sec, un peu. Encore soif. Un tout petit peu, alors. Je lève le store. Le store monte, avec un bruit de toile. La lumière arrive, plus douce qu'à midi. Aniss verse trois gouttes, pas plus. La terre s'assombrit, juste au milieu. Voilà. Eau, et de la lumière. Merci, Aniss. Tu as regardé deux fois. Matin, et soir. Oui. Une feuille tient plus droit, maintenant. Aniss la pince, tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gaston a arrosé. Il y a de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt; et de la lumière. Maman, l'adulte, était là. Papa a ouvert le store.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le soir, la cuisine est orange. Les tomates attendent dans le plat. Le basilic. Aniss touche la terre. Le dessus est encore sec, un peu. Encore soif. Un tout petit peu, alors. Je lève le store. Le store monte, avec un bruit de toile. La lumière arrive, plus douce qu'à midi. Aniss verse trois gouttes, pas plus. La terre s'assombrit, juste au milieu. Voilà. Eau, et de la lumière. Merci, Aniss. Tu as regardé deux fois. Matin, et soir. Oui. Une feuille tient plus droit, maintenant. Aniss la pince, tout doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1598,7 +1639,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1674,10 +1715,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gaston a arrosé. Il y a de l'eau et de la lumière. Maman, l'adulte, était là. Papa a ouvert le store.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le soir, la cuisine est orange.
+narrateur|Les tomates attendent dans le plat.
+enfant-m|Le basilic.
+narrateur|Aniss touche la terre.
+narrateur|Le dessus est encore sec, un peu.
+enfant-m|Encore soif.
+maman|Un tout petit peu, alors.
+papa|Je lève le store.
+narrateur|Le store monte, avec un bruit de toile.
+narrateur|La lumière arrive, plus douce qu'à midi.
+narrateur|Aniss verse trois gouttes, pas plus.
+narrateur|La terre s'assombrit, juste au milieu.
+papa|Voilà.
+papa|Eau, et de la lumière.
+maman|Merci, Aniss.
+maman|Tu as regardé deux fois.
+enfant-m|Matin, et soir.
+papa|Oui.
+narrateur|Une feuille tient plus droit, maintenant.
+narrateur|Aniss la pince, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,12 +1761,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gaston essuie ses mains. Le basilic brille.</t>
+          <t>L'odeur saute, verte, sur les doigts. Pour les tomates. On coupe deux feuilles ? Deux. Maman coupe. Le couteau fait un clic de bois. Les feuilles tombent sur le rouge. Tu froisses un peu ? Fffff. Aniss souffle. L'odeur se mêle aux tomates. C'est ce que tu voulais, ce matin. Oui. Le store reste ouvert, un peu. Pour la nuit, pas trop d'air. Aniss essuie ses mains au torchon. Le torchon sent le vert, maintenant. On goûte ? On goûte.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gaston essuie ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Le basilic brille.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'odeur saute, verte, sur les doigts. Pour les tomates. On coupe deux feuilles ? Deux. Maman coupe. Le couteau fait un clic de bois. Les feuilles tombent sur le rouge. Tu froisses un peu ? Fffff. Aniss souffle. L'odeur se mêle aux tomates. C'est ce que tu voulais, ce matin. Oui. Le store reste ouvert, un peu. Pour la nuit, pas trop d'air. Aniss essuie ses mains au torchon. Le torchon sent le vert, maintenant. On goûte ? On goûte.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1770,7 +1829,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1842,10 +1901,27 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Gaston essuie ses mains. Le basilic brille.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|L'odeur saute, verte, sur les doigts.
+enfant-m|Pour les tomates.
+maman|On coupe deux feuilles ?
+enfant-m|Deux.
+narrateur|Maman coupe.
+narrateur|Le couteau fait un clic de bois.
+narrateur|Les feuilles tombent sur le rouge.
+papa|Tu froisses un peu ?
+enfant-m|Fffff.
+narrateur|Aniss souffle.
+narrateur|L'odeur se mêle aux tomates.
+maman|C'est ce que tu voulais, ce matin.
+enfant-m|Oui.
+papa|Le store reste ouvert, un peu.
+papa|Pour la nuit, pas trop d'air.
+narrateur|Aniss essuie ses mains au torchon.
+narrateur|Le torchon sent le vert, maintenant.
+maman|On goûte ?
+enfant-m|On goûte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss croque une tomate. Le basilic est dessus, tout frais. Matin, et soir. Oui. Deux fois, tout doux. Le basilic du soir sent les tomates.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss croque une tomate. Le basilic est dessus, tout frais. Matin, et soir. Oui. Deux fois, tout doux. Le basilic du soir sent les tomates.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1931,14 +2007,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2010,10 +2086,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Aniss croque une tomate.
+narrateur|Le basilic est dessus, tout frais.
+enfant-m|Matin, et soir.
+maman|Oui.
+papa|Deux fois, tout doux.
+narrateur|Le basilic du soir sent les tomates.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2150,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-07.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fenêtre de la cuisine</t>
+          <t>fenêtre de la cuisine, matin puis soir</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gaston, maman, papa</t>
+          <t>Aniss, maman, papa</t>
         </is>
       </c>
     </row>
